--- a/batchtest/Results/AnhDThe187386/TC4/GradeDetail.xlsx
+++ b/batchtest/Results/AnhDThe187386/TC4/GradeDetail.xlsx
@@ -71,6 +71,18 @@
     <x:t>ActualExcerpt</x:t>
   </x:si>
   <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>StartClient</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StartServer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> S001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Console</x:t>
   </x:si>
   <x:si>
@@ -129,9 +141,6 @@
   </x:si>
   <x:si>
     <x:t>NetworkResult</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
   <x:si>
     <x:t>TCP</x:t>
@@ -554,11 +563,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:Q1"/>
+  <x:dimension ref="A1:Q4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="2" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.424911" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.282054" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.996339" style="0" customWidth="1"/>
@@ -625,6 +634,39 @@
       </x:c>
       <x:c r="Q1" s="1" t="s">
         <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:17">
+      <x:c r="A2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:17">
+      <x:c r="A3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:17">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -669,7 +711,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
         <x:v>1</x:v>
@@ -720,7 +762,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -765,7 +807,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
         <x:v>1</x:v>
@@ -816,7 +858,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -877,55 +919,55 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="Q1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="R1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:18">
@@ -933,55 +975,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -989,55 +1031,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1045,55 +1087,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R4" s="2" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="R4" s="2" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1101,55 +1143,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1157,55 +1199,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R6" s="2" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="R6" s="2" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1213,55 +1255,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1269,55 +1311,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R8" s="2" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="R8" s="2" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1325,55 +1367,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R9" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1381,55 +1423,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R10" s="2" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="R10" s="2" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1437,55 +1479,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R11" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1493,55 +1535,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R12" s="2" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="R12" s="2" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
